--- a/Datalist/PVZ3DTowerExcel.xlsx
+++ b/Datalist/PVZ3DTowerExcel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ZZZthing\杂项\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnrealProject\PVZ3D\Datalist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075BA49E-A4A9-4DF1-BDB0-B195BD1FB987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE50692-31AE-47D0-B0D3-BE561EE2F816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>TowerID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -118,6 +118,10 @@
   </si>
   <si>
     <t>103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -489,7 +493,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -524,7 +528,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
@@ -559,7 +563,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>

--- a/Datalist/PVZ3DTowerExcel.xlsx
+++ b/Datalist/PVZ3DTowerExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnrealProject\PVZ3D\Datalist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE50692-31AE-47D0-B0D3-BE561EE2F816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737C48F5-7959-4281-AA3A-E47580166F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24330" yWindow="2865" windowWidth="23205" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -448,46 +448,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="5" width="13.77734375" customWidth="1"/>
-    <col min="6" max="6" width="17.109375" customWidth="1"/>
-    <col min="8" max="8" width="20.88671875" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" customWidth="1"/>
-    <col min="10" max="10" width="17.109375" customWidth="1"/>
+    <col min="1" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="5" width="13.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="20.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.109375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -498,10 +501,10 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -516,13 +519,13 @@
       <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>1000</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>3</v>
       </c>
     </row>
@@ -533,10 +536,10 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -551,13 +554,13 @@
       <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>1000</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>3</v>
       </c>
     </row>
@@ -568,10 +571,10 @@
       <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -586,79 +589,15 @@
       <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>10</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
